--- a/5. Other/Đề xuất mua hàng/Năm 2026/Đề Xuất Mua Vật Tư BH-SX Cập Nhật Thêm 0707_090726.xlsx
+++ b/5. Other/Đề xuất mua hàng/Năm 2026/Đề Xuất Mua Vật Tư BH-SX Cập Nhật Thêm 0707_090726.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Đề xuất mua hàng\Năm 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0EA989-26C3-47C5-998B-DF59DA1AF7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C419C6B-72D3-4163-834A-2C20C5C7C8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DeXuatVatTu" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -123,23 +123,23 @@
     <t>Mũi Tua Vít Phillips PH1 Hex Shank S2 50mm Φ 4</t>
   </si>
   <si>
-    <t>https://sl1nk.com/lponmzt</t>
-  </si>
-  <si>
-    <t>https://l1nq.com/nwsw0j1</t>
-  </si>
-  <si>
     <t>Xăng vệ sinh bo mạch PCB chai thủy tinh 350ml</t>
   </si>
   <si>
-    <t>https://l1nq.com/3ukvy51</t>
+    <t>https://shopee.vn/Tua-v%C3%ADt-nh%E1%BB%8F-2-c%E1%BA%A1nh-4-c%E1%BA%A1nh-c%C3%B3-nam-ch%C3%A2m-i.313990598.25367050698?extraParams=%7B%22display_model_id%22%3A204947377381%2C%22model_selection_logic%22%3A3%7D&amp;sp_atk=6e0c4668-1025-4f4e-841b-571d9e87e9e9&amp;xptdk=6e0c4668-1025-4f4e-841b-571d9e87e9e9</t>
+  </si>
+  <si>
+    <t>https://linhkienchatluong.vn/urldung-dich-tay-rua/xang-ve-sinh-bo-mach-pcb-chai-thuy-tinh-350ml_sp2397_ct4693.aspx</t>
+  </si>
+  <si>
+    <t>https://shopee.vn/1-C%C3%A1i-M%C5%A9i-Tua-V%C3%ADt-Phillips-PH00-PH0-PH1-PH2-T%E1%BB%AB-1-4-in.-Hex-Shank-S2-Steel-50-70mm-S%E1%BB%ADa-ch%E1%BB%AFa-%C4%91%E1%BA%A7u-l%C3%B4-%C4%91i%E1%BB%87n-d%C3%A0i-i.1655135525.54602585069?extraParams=%7B%22display_model_id%22%3A320249517174%2C%22model_selection_logic%22%3A3%7D&amp;sp_atk=896338a7-e7bc-4ab8-ace5-dcd92c0f9ac0&amp;xptdk=896338a7-e7bc-4ab8-ace5-dcd92c0f9ac0&amp;gidzl=0VxdAxe5l0G3uE4iiHYw00BbxYsc7hTG7BU-UASQi50KvkzsfnYqNXwskNRs6x1UJk7e9MAAosmVkGAx1G</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,8 +215,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,8 +235,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -381,12 +392,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -433,16 +459,28 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -478,19 +516,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,8 +602,8 @@
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -617,8 +646,8 @@
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1018,50 +1047,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20"/>
-      <c r="B1" s="20"/>
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
       <c r="C1" s="8"/>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="21" t="s">
+      <c r="E1" s="27"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="21"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
       <c r="C2" s="8"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="21" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="21"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="21" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="21"/>
+      <c r="H3" s="25"/>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="10"/>
@@ -1070,46 +1099,46 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="20"/>
+      <c r="D5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="32"/>
-    </row>
-    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>1</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="14"/>
@@ -1123,15 +1152,15 @@
         <v>6</v>
       </c>
       <c r="G7" s="14"/>
-      <c r="H7" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="H7" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14" t="s">
         <v>30</v>
@@ -1144,14 +1173,14 @@
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>3</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="22"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14" t="s">
         <v>26</v>
@@ -1167,14 +1196,14 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>4</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>24</v>
@@ -1184,14 +1213,14 @@
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>5</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="23"/>
       <c r="C11" s="11"/>
       <c r="D11" s="12" t="s">
         <v>23</v>
@@ -1230,40 +1259,40 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18" t="s">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18" t="s">
+      <c r="D14" s="19"/>
+      <c r="E14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18" t="s">
+      <c r="F14" s="19"/>
+      <c r="G14" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="18"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="35"/>
+      <c r="C15" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="35"/>
+      <c r="E15" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17" t="s">
+      <c r="F15" s="35"/>
+      <c r="G15" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="17"/>
+      <c r="H15" s="35"/>
     </row>
     <row r="16" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
@@ -1296,32 +1325,32 @@
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
     </row>
     <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18" t="s">
+      <c r="B20" s="19"/>
+      <c r="C20" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18" t="s">
+      <c r="D20" s="19"/>
+      <c r="E20" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18" t="s">
+      <c r="F20" s="19"/>
+      <c r="G20" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="18"/>
+      <c r="H20" s="19"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -1345,6 +1374,23 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="D1:F3"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="H5:H6"/>
@@ -1357,32 +1403,9 @@
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="B7:B11"/>
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="H7" r:id="rId1" xr:uid="{885ABE68-3FBC-4E71-AD94-4F9F95BD8078}"/>
-    <hyperlink ref="H8" r:id="rId2" xr:uid="{CCBFE382-BFD1-4E49-B233-D7C02D4131BC}"/>
-    <hyperlink ref="H9" r:id="rId3" xr:uid="{8C7DD660-AE3A-4FD2-8D31-1EC6D928F282}"/>
-    <hyperlink ref="H10" r:id="rId4" xr:uid="{5B098EB4-BE72-4127-A74C-6FBDB3FD7A7A}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId5"/>
-  <drawing r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>